--- a/data/pupil/3_processed/15_semantic_similarity/event/sub_1009_cosine_similarity.xlsx
+++ b/data/pupil/3_processed/15_semantic_similarity/event/sub_1009_cosine_similarity.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F56"/>
+  <dimension ref="A1:G56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,25 +436,30 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>Pool Party</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>Sea Ice</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Natalie Wood</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Grandfather Clocks</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Impatient Billionaire</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Dont Look</t>
         </is>
@@ -465,18 +470,21 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2" t="n">
         <v>0.4294995665550232</v>
       </c>
-      <c r="C2" t="n">
+      <c r="D2" t="n">
         <v>0.2337323278188705</v>
       </c>
-      <c r="D2" t="n">
+      <c r="E2" t="n">
         <v>0.2791692316532135</v>
       </c>
-      <c r="E2" t="n">
+      <c r="F2" t="n">
         <v>0.7144814729690552</v>
       </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
         <v>0.2716613411903381</v>
       </c>
     </row>
@@ -485,18 +493,21 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" t="n">
         <v>0.5828983783721924</v>
       </c>
-      <c r="C3" t="n">
+      <c r="D3" t="n">
         <v>0.40337735414505</v>
       </c>
-      <c r="D3" t="n">
+      <c r="E3" t="n">
         <v>0.243187427520752</v>
       </c>
-      <c r="E3" t="n">
+      <c r="F3" t="n">
         <v>0.4127987325191498</v>
       </c>
-      <c r="F3" t="n">
+      <c r="G3" t="n">
         <v>0.2227866649627686</v>
       </c>
     </row>
@@ -505,18 +516,21 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" t="n">
         <v>0.5978657007217407</v>
       </c>
-      <c r="C4" t="n">
+      <c r="D4" t="n">
         <v>0.5011774897575378</v>
       </c>
-      <c r="D4" t="n">
+      <c r="E4" t="n">
         <v>0.1526671499013901</v>
       </c>
-      <c r="E4" t="n">
+      <c r="F4" t="n">
         <v>0.5997380614280701</v>
       </c>
-      <c r="F4" t="n">
+      <c r="G4" t="n">
         <v>0.3548216223716736</v>
       </c>
     </row>
@@ -525,18 +539,21 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" t="n">
         <v>0.5418573021888733</v>
       </c>
-      <c r="C5" t="n">
+      <c r="D5" t="n">
         <v>0.2954616546630859</v>
       </c>
-      <c r="D5" t="n">
+      <c r="E5" t="n">
         <v>0.5318518877029419</v>
       </c>
-      <c r="E5" t="n">
+      <c r="F5" t="n">
         <v>0.4442755877971649</v>
       </c>
-      <c r="F5" t="n">
+      <c r="G5" t="n">
         <v>0.2077684849500656</v>
       </c>
     </row>
@@ -545,18 +562,21 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" t="n">
         <v>0.4375262856483459</v>
       </c>
-      <c r="C6" t="n">
+      <c r="D6" t="n">
         <v>0.5203588008880615</v>
       </c>
-      <c r="D6" t="n">
+      <c r="E6" t="n">
         <v>0.2139915376901627</v>
       </c>
-      <c r="E6" t="n">
+      <c r="F6" t="n">
         <v>0.4196350872516632</v>
       </c>
-      <c r="F6" t="n">
+      <c r="G6" t="n">
         <v>0.2683350145816803</v>
       </c>
     </row>
@@ -568,15 +588,18 @@
         <v>0</v>
       </c>
       <c r="C7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" t="n">
         <v>0.1780542135238647</v>
       </c>
-      <c r="D7" t="n">
+      <c r="E7" t="n">
         <v>0.6376469731330872</v>
       </c>
-      <c r="E7" t="n">
+      <c r="F7" t="n">
         <v>0.5965272784233093</v>
       </c>
-      <c r="F7" t="n">
+      <c r="G7" t="n">
         <v>0.4734465777873993</v>
       </c>
     </row>
@@ -588,15 +611,18 @@
         <v>0</v>
       </c>
       <c r="C8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" t="n">
         <v>0.1854559183120728</v>
       </c>
-      <c r="D8" t="n">
+      <c r="E8" t="n">
         <v>0.3894950747489929</v>
       </c>
-      <c r="E8" t="n">
+      <c r="F8" t="n">
         <v>0.4495012760162354</v>
       </c>
-      <c r="F8" t="n">
+      <c r="G8" t="n">
         <v>0.413002997636795</v>
       </c>
     </row>
@@ -608,15 +634,18 @@
         <v>0</v>
       </c>
       <c r="C9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" t="n">
         <v>0.4637294411659241</v>
       </c>
-      <c r="D9" t="n">
+      <c r="E9" t="n">
         <v>0.5747751593589783</v>
       </c>
-      <c r="E9" t="n">
+      <c r="F9" t="n">
         <v>0.5242466330528259</v>
       </c>
-      <c r="F9" t="n">
+      <c r="G9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -625,18 +654,21 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" t="n">
         <v>0.3807284235954285</v>
       </c>
-      <c r="C10" t="n">
+      <c r="D10" t="n">
         <v>0.2987549602985382</v>
       </c>
-      <c r="D10" t="n">
+      <c r="E10" t="n">
         <v>0.4664921164512634</v>
       </c>
-      <c r="E10" t="n">
+      <c r="F10" t="n">
         <v>0.4375985860824585</v>
       </c>
-      <c r="F10" t="n">
+      <c r="G10" t="n">
         <v>0.3874819874763489</v>
       </c>
     </row>
@@ -645,18 +677,21 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" t="n">
         <v>0.6655089259147644</v>
       </c>
-      <c r="C11" t="n">
+      <c r="D11" t="n">
         <v>0.4243554472923279</v>
       </c>
-      <c r="D11" t="n">
+      <c r="E11" t="n">
         <v>0.4130183458328247</v>
       </c>
-      <c r="E11" t="n">
+      <c r="F11" t="n">
         <v>0.3568499982357025</v>
       </c>
-      <c r="F11" t="n">
+      <c r="G11" t="n">
         <v>0.3433550298213959</v>
       </c>
     </row>
@@ -665,18 +700,21 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" t="n">
         <v>0.5527963638305664</v>
       </c>
-      <c r="C12" t="n">
+      <c r="D12" t="n">
         <v>0.08452099561691284</v>
       </c>
-      <c r="D12" t="n">
+      <c r="E12" t="n">
         <v>0.4110657870769501</v>
       </c>
-      <c r="E12" t="n">
+      <c r="F12" t="n">
         <v>0.343591570854187</v>
       </c>
-      <c r="F12" t="n">
+      <c r="G12" t="n">
         <v>0.07559052854776382</v>
       </c>
     </row>
@@ -685,18 +723,21 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" t="n">
         <v>0.5101481080055237</v>
       </c>
-      <c r="C13" t="n">
-        <v>0</v>
-      </c>
       <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="n">
         <v>0.6751312613487244</v>
       </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
       <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
         <v>0.2016744911670685</v>
       </c>
     </row>
@@ -705,18 +746,21 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" t="n">
         <v>0.2947934567928314</v>
       </c>
-      <c r="C14" t="n">
+      <c r="D14" t="n">
         <v>0.3328136801719666</v>
       </c>
-      <c r="D14" t="n">
+      <c r="E14" t="n">
         <v>0.4495261311531067</v>
       </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
       <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
         <v>0.3393485248088837</v>
       </c>
     </row>
@@ -728,15 +772,18 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" t="n">
         <v>0.4086624979972839</v>
       </c>
-      <c r="D15" t="n">
+      <c r="E15" t="n">
         <v>0.3558070361614227</v>
       </c>
-      <c r="E15" t="n">
+      <c r="F15" t="n">
         <v>0.1533104181289673</v>
       </c>
-      <c r="F15" t="n">
+      <c r="G15" t="n">
         <v>0.219125360250473</v>
       </c>
     </row>
@@ -748,15 +795,18 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" t="n">
         <v>0.2528930902481079</v>
       </c>
-      <c r="D16" t="n">
+      <c r="E16" t="n">
         <v>0.4706943035125732</v>
       </c>
-      <c r="E16" t="n">
+      <c r="F16" t="n">
         <v>0.1382004618644714</v>
       </c>
-      <c r="F16" t="n">
+      <c r="G16" t="n">
         <v>0.1998074352741241</v>
       </c>
     </row>
@@ -768,15 +818,18 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" t="n">
         <v>0.4808345139026642</v>
       </c>
-      <c r="D17" t="n">
+      <c r="E17" t="n">
         <v>0.5714180469512939</v>
       </c>
-      <c r="E17" t="n">
+      <c r="F17" t="n">
         <v>0.07071785628795624</v>
       </c>
-      <c r="F17" t="n">
+      <c r="G17" t="n">
         <v>0.194867342710495</v>
       </c>
     </row>
@@ -788,15 +841,18 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" t="n">
         <v>0.2399840652942657</v>
       </c>
-      <c r="D18" t="n">
+      <c r="E18" t="n">
         <v>0.5253633260726929</v>
       </c>
-      <c r="E18" t="n">
+      <c r="F18" t="n">
         <v>0.1735620945692062</v>
       </c>
-      <c r="F18" t="n">
+      <c r="G18" t="n">
         <v>0.3971039354801178</v>
       </c>
     </row>
@@ -808,13 +864,16 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" t="n">
         <v>0.4698607325553894</v>
       </c>
-      <c r="D19" t="n">
+      <c r="E19" t="n">
         <v>0.354841411113739</v>
       </c>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="n">
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="n">
         <v>0.2814283668994904</v>
       </c>
     </row>
@@ -826,13 +885,16 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" t="n">
         <v>0.1430184245109558</v>
       </c>
-      <c r="D20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="n">
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="n">
         <v>0</v>
       </c>
     </row>
@@ -841,16 +903,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" t="n">
         <v>0.6028308868408203</v>
       </c>
-      <c r="C21" t="n">
+      <c r="D21" t="n">
         <v>0.1586644947528839</v>
       </c>
-      <c r="D21" t="n">
+      <c r="E21" t="n">
         <v>0.492741584777832</v>
       </c>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="n">
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="n">
         <v>0.3499559462070465</v>
       </c>
     </row>
@@ -858,17 +923,18 @@
       <c r="A22" t="n">
         <v>21</v>
       </c>
-      <c r="B22" t="n">
-        <v>0</v>
-      </c>
+      <c r="B22" t="inlineStr"/>
       <c r="C22" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" t="n">
         <v>0.2829847037792206</v>
       </c>
-      <c r="D22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="n">
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="n">
         <v>0.2019456326961517</v>
       </c>
     </row>
@@ -876,17 +942,18 @@
       <c r="A23" t="n">
         <v>22</v>
       </c>
-      <c r="B23" t="n">
-        <v>0</v>
-      </c>
+      <c r="B23" t="inlineStr"/>
       <c r="C23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" t="n">
         <v>0.4542528092861176</v>
       </c>
-      <c r="D23" t="n">
+      <c r="E23" t="n">
         <v>0.4473287463188171</v>
       </c>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="n">
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="n">
         <v>0</v>
       </c>
     </row>
@@ -894,17 +961,18 @@
       <c r="A24" t="n">
         <v>23</v>
       </c>
-      <c r="B24" t="n">
-        <v>0</v>
-      </c>
+      <c r="B24" t="inlineStr"/>
       <c r="C24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" t="n">
         <v>0.1053957268595695</v>
       </c>
-      <c r="D24" t="n">
+      <c r="E24" t="n">
         <v>0.714228630065918</v>
       </c>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="n">
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="n">
         <v>0</v>
       </c>
     </row>
@@ -913,14 +981,15 @@
         <v>24</v>
       </c>
       <c r="B25" t="inlineStr"/>
-      <c r="C25" t="n">
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="n">
         <v>0.1033719927072525</v>
       </c>
-      <c r="D25" t="n">
+      <c r="E25" t="n">
         <v>0.6245597004890442</v>
       </c>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="n">
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="n">
         <v>0.272542804479599</v>
       </c>
     </row>
@@ -929,14 +998,15 @@
         <v>25</v>
       </c>
       <c r="B26" t="inlineStr"/>
-      <c r="C26" t="n">
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="n">
         <v>0.490309864282608</v>
       </c>
-      <c r="D26" t="n">
+      <c r="E26" t="n">
         <v>0.5505766272544861</v>
       </c>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="n">
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="n">
         <v>0.3931445181369781</v>
       </c>
     </row>
@@ -945,14 +1015,15 @@
         <v>26</v>
       </c>
       <c r="B27" t="inlineStr"/>
-      <c r="C27" t="n">
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="n">
         <v>0.211721658706665</v>
       </c>
-      <c r="D27" t="n">
+      <c r="E27" t="n">
         <v>0.373896062374115</v>
       </c>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="n">
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="n">
         <v>0.4028781950473785</v>
       </c>
     </row>
@@ -961,14 +1032,15 @@
         <v>27</v>
       </c>
       <c r="B28" t="inlineStr"/>
-      <c r="C28" t="n">
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="n">
         <v>0.4097397327423096</v>
       </c>
-      <c r="D28" t="n">
+      <c r="E28" t="n">
         <v>0.3163525462150574</v>
       </c>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="n">
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="n">
         <v>0</v>
       </c>
     </row>
@@ -977,14 +1049,15 @@
         <v>28</v>
       </c>
       <c r="B29" t="inlineStr"/>
-      <c r="C29" t="n">
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="n">
         <v>0.4232998192310333</v>
       </c>
-      <c r="D29" t="n">
+      <c r="E29" t="n">
         <v>0.5025941133499146</v>
       </c>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="n">
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="n">
         <v>0</v>
       </c>
     </row>
@@ -993,14 +1066,15 @@
         <v>29</v>
       </c>
       <c r="B30" t="inlineStr"/>
-      <c r="C30" t="n">
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="n">
         <v>0.03929498419165611</v>
       </c>
-      <c r="D30" t="n">
+      <c r="E30" t="n">
         <v>0.6479108929634094</v>
       </c>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="n">
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="n">
         <v>0.09426438808441162</v>
       </c>
     </row>
@@ -1009,12 +1083,13 @@
         <v>30</v>
       </c>
       <c r="B31" t="inlineStr"/>
-      <c r="C31" t="n">
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="n">
         <v>0.2473711222410202</v>
       </c>
-      <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr"/>
-      <c r="F31" t="n">
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="n">
         <v>0.06584350019693375</v>
       </c>
     </row>
@@ -1023,12 +1098,13 @@
         <v>31</v>
       </c>
       <c r="B32" t="inlineStr"/>
-      <c r="C32" t="n">
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="n">
         <v>0.5102634429931641</v>
       </c>
-      <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr"/>
-      <c r="F32" t="n">
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1037,12 +1113,13 @@
         <v>32</v>
       </c>
       <c r="B33" t="inlineStr"/>
-      <c r="C33" t="n">
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="n">
         <v>0.3705269992351532</v>
       </c>
-      <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr"/>
-      <c r="F33" t="n">
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="n">
         <v>0.369886726140976</v>
       </c>
     </row>
@@ -1051,12 +1128,13 @@
         <v>33</v>
       </c>
       <c r="B34" t="inlineStr"/>
-      <c r="C34" t="n">
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="n">
         <v>0.1541923433542252</v>
       </c>
-      <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr"/>
-      <c r="F34" t="n">
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="n">
         <v>0.3163677752017975</v>
       </c>
     </row>
@@ -1065,12 +1143,13 @@
         <v>34</v>
       </c>
       <c r="B35" t="inlineStr"/>
-      <c r="C35" t="n">
+      <c r="C35" t="inlineStr"/>
+      <c r="D35" t="n">
         <v>0.12529157102108</v>
       </c>
-      <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr"/>
-      <c r="F35" t="n">
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="n">
         <v>0.6272724270820618</v>
       </c>
     </row>
@@ -1079,12 +1158,13 @@
         <v>35</v>
       </c>
       <c r="B36" t="inlineStr"/>
-      <c r="C36" t="n">
+      <c r="C36" t="inlineStr"/>
+      <c r="D36" t="n">
         <v>0.4394429922103882</v>
       </c>
-      <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr"/>
-      <c r="F36" t="n">
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="n">
         <v>0.5614150762557983</v>
       </c>
     </row>
@@ -1093,12 +1173,13 @@
         <v>36</v>
       </c>
       <c r="B37" t="inlineStr"/>
-      <c r="C37" t="n">
+      <c r="C37" t="inlineStr"/>
+      <c r="D37" t="n">
         <v>0.4165959358215332</v>
       </c>
-      <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr"/>
-      <c r="F37" t="n">
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="n">
         <v>0.01297527924180031</v>
       </c>
     </row>
@@ -1107,12 +1188,13 @@
         <v>37</v>
       </c>
       <c r="B38" t="inlineStr"/>
-      <c r="C38" t="n">
+      <c r="C38" t="inlineStr"/>
+      <c r="D38" t="n">
         <v>0.4094805419445038</v>
       </c>
-      <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr"/>
-      <c r="F38" t="n">
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="n">
         <v>0.03061114251613617</v>
       </c>
     </row>
@@ -1121,12 +1203,13 @@
         <v>38</v>
       </c>
       <c r="B39" t="inlineStr"/>
-      <c r="C39" t="n">
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" t="n">
         <v>0.3207410573959351</v>
       </c>
-      <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr"/>
-      <c r="F39" t="n">
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="n">
         <v>0.3644402921199799</v>
       </c>
     </row>
@@ -1135,12 +1218,13 @@
         <v>39</v>
       </c>
       <c r="B40" t="inlineStr"/>
-      <c r="C40" t="n">
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" t="n">
         <v>0.431597113609314</v>
       </c>
-      <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr"/>
-      <c r="F40" t="n">
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="n">
         <v>0.2743464708328247</v>
       </c>
     </row>
@@ -1149,12 +1233,13 @@
         <v>40</v>
       </c>
       <c r="B41" t="inlineStr"/>
-      <c r="C41" t="n">
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" t="n">
         <v>0.3338581323623657</v>
       </c>
-      <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr"/>
-      <c r="F41" t="n">
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="n">
         <v>0.5393668413162231</v>
       </c>
     </row>
@@ -1163,12 +1248,13 @@
         <v>41</v>
       </c>
       <c r="B42" t="inlineStr"/>
-      <c r="C42" t="n">
+      <c r="C42" t="inlineStr"/>
+      <c r="D42" t="n">
         <v>0.185919463634491</v>
       </c>
-      <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr"/>
-      <c r="F42" t="n">
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="n">
         <v>0.348103791475296</v>
       </c>
     </row>
@@ -1177,168 +1263,182 @@
         <v>42</v>
       </c>
       <c r="B43" t="inlineStr"/>
-      <c r="C43" t="n">
+      <c r="C43" t="inlineStr"/>
+      <c r="D43" t="n">
         <v>0.243580088019371</v>
       </c>
-      <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
         <v>43</v>
       </c>
       <c r="B44" t="inlineStr"/>
-      <c r="C44" t="n">
+      <c r="C44" t="inlineStr"/>
+      <c r="D44" t="n">
         <v>0.3858554065227509</v>
       </c>
-      <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
         <v>44</v>
       </c>
       <c r="B45" t="inlineStr"/>
-      <c r="C45" t="n">
+      <c r="C45" t="inlineStr"/>
+      <c r="D45" t="n">
         <v>0.1441861093044281</v>
       </c>
-      <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
         <v>45</v>
       </c>
       <c r="B46" t="inlineStr"/>
-      <c r="C46" t="n">
+      <c r="C46" t="inlineStr"/>
+      <c r="D46" t="n">
         <v>0.4040346741676331</v>
       </c>
-      <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
         <v>46</v>
       </c>
       <c r="B47" t="inlineStr"/>
-      <c r="C47" t="n">
+      <c r="C47" t="inlineStr"/>
+      <c r="D47" t="n">
         <v>0.1061198338866234</v>
       </c>
-      <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
         <v>47</v>
       </c>
       <c r="B48" t="inlineStr"/>
-      <c r="C48" t="n">
+      <c r="C48" t="inlineStr"/>
+      <c r="D48" t="n">
         <v>0.1056817620992661</v>
       </c>
-      <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
         <v>48</v>
       </c>
       <c r="B49" t="inlineStr"/>
-      <c r="C49" t="n">
+      <c r="C49" t="inlineStr"/>
+      <c r="D49" t="n">
         <v>0.2632349133491516</v>
       </c>
-      <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
         <v>49</v>
       </c>
       <c r="B50" t="inlineStr"/>
-      <c r="C50" t="n">
+      <c r="C50" t="inlineStr"/>
+      <c r="D50" t="n">
         <v>0.1730508655309677</v>
       </c>
-      <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
         <v>50</v>
       </c>
       <c r="B51" t="inlineStr"/>
-      <c r="C51" t="n">
+      <c r="C51" t="inlineStr"/>
+      <c r="D51" t="n">
         <v>0.1175237074494362</v>
       </c>
-      <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
         <v>51</v>
       </c>
       <c r="B52" t="inlineStr"/>
-      <c r="C52" t="n">
+      <c r="C52" t="inlineStr"/>
+      <c r="D52" t="n">
         <v>0.1950897574424744</v>
       </c>
-      <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
         <v>52</v>
       </c>
       <c r="B53" t="inlineStr"/>
-      <c r="C53" t="n">
+      <c r="C53" t="inlineStr"/>
+      <c r="D53" t="n">
         <v>0.25294029712677</v>
       </c>
-      <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
         <v>53</v>
       </c>
       <c r="B54" t="inlineStr"/>
-      <c r="C54" t="n">
+      <c r="C54" t="inlineStr"/>
+      <c r="D54" t="n">
         <v>0.2579851746559143</v>
       </c>
-      <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
         <v>54</v>
       </c>
       <c r="B55" t="inlineStr"/>
-      <c r="C55" t="n">
+      <c r="C55" t="inlineStr"/>
+      <c r="D55" t="n">
         <v>0.2277675569057465</v>
       </c>
-      <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
         <v>55</v>
       </c>
       <c r="B56" t="inlineStr"/>
-      <c r="C56" t="n">
+      <c r="C56" t="inlineStr"/>
+      <c r="D56" t="n">
         <v>0.2714318633079529</v>
       </c>
-      <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
